--- a/用卷/xlsx/常规科目/1989.xlsx
+++ b/用卷/xlsx/常规科目/1989.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183DF96F-4204-420A-A9C2-D9146AD0F3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEACE7E-835C-449D-9F16-956455A1B287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1132,7 +1132,7 @@
       <c r="B32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="7" t="s">
         <v>46</v>
       </c>
     </row>
